--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +745,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +780,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +815,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +834,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +900,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +935,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +970,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +986,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +1017,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1052,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1071,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1102,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1137,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1172,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1207,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1277,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1312,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1347,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1487,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1522,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1557,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1592,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1627,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1701,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>312300</v>
+      </c>
+      <c r="F41" s="3">
         <v>279400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>281400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>165500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>166700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>153600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>160400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>149600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,211 +1767,259 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>893700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>962700</v>
+      </c>
+      <c r="F43" s="3">
         <v>885600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>891700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>644600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>620100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>630400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>664400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>595300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>746000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>803700</v>
+      </c>
+      <c r="F44" s="3">
         <v>736500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>741600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>537900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>550000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>580700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>561600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>546400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F45" s="3">
         <v>35300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>35500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>55200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>11500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1945800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2096100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1936800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1950200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1403200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1339100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1374000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1398700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1327700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F47" s="3">
         <v>27500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>27700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>30400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>29900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>32100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>31800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>32000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3073100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3310600</v>
+      </c>
+      <c r="F48" s="3">
         <v>3071100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3092400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1827800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1798400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1808000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1770200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1734800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10378100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11180200</v>
+      </c>
+      <c r="F49" s="3">
         <v>10996800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11072700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>672100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>647100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>669000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>670700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>675000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>27500</v>
+      </c>
+      <c r="F52" s="3">
         <v>37000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>37200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>15600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>17600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>17400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>17400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>17800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15732100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16948000</v>
+      </c>
+      <c r="F54" s="3">
         <v>16342200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16455100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4210300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4047700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4137600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4124800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4020600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2221,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>471900</v>
+      </c>
+      <c r="F57" s="3">
         <v>370500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>373100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>239600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>207100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>193600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>211800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>268500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>275800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>297100</v>
+      </c>
+      <c r="F58" s="3">
         <v>982200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>989000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>477500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>350900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>480800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>485300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>437100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>412900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>444800</v>
+      </c>
+      <c r="F59" s="3">
         <v>394400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>397100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>238200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>324700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>327600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>340700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>195300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1126700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1213800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1747100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1759200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1076900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>882700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1002000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1037800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1000400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1584400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1706900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1149100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1157100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>676400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>663800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>710200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>722000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>561400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>44300</v>
+      </c>
+      <c r="F62" s="3">
         <v>23400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>14800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>134200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>133100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>162200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>158500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4161500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4483200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4550700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4582200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2082100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1935800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2115000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2187300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1976300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11421900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12304700</v>
+      </c>
+      <c r="F72" s="3">
         <v>11678700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>11759300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2039800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1959200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1890900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1791200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1876700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11570600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12464900</v>
+      </c>
+      <c r="F76" s="3">
         <v>11789900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11871300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2072900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2054400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1962100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1878200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1988100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +2932,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +3007,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3026,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F83" s="3">
         <v>-52300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>52100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>154900</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>53000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>158500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>254600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>274300</v>
+      </c>
+      <c r="F89" s="3">
         <v>282900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>284900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>166400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>225000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>165700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>45800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>83900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3286,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-72400</v>
+        <v>-105100</v>
       </c>
       <c r="E91" s="3">
-        <v>-72900</v>
+        <v>-113300</v>
       </c>
       <c r="F91" s="3">
         <v>-72400</v>
       </c>
       <c r="G91" s="3">
+        <v>-72900</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-62000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-75400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-60500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-119300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-29400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-29600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-89400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-68900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-103300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-49400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-129000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3441,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>69600</v>
+      </c>
+      <c r="F96" s="3">
         <v>66900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>67400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>172500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>242400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3577,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-170700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-183900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-201400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-82300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-138600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-66800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>14400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-6500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>9300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F102" s="3">
         <v>59500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>59900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-48300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>48000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -656,44 +656,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45473</v>
       </c>
       <c r="G7" s="2">
         <v>45382</v>
@@ -708,16 +708,19 @@
         <v>45107</v>
       </c>
       <c r="K7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +754,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +792,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +848,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +922,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +960,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +998,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1013,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,8 +1049,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,8 +1087,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1105,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1108,8 +1141,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1179,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,8 +1217,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,8 +1255,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1293,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,8 +1331,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1318,8 +1369,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1353,8 +1407,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1483,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1559,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +1597,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1563,8 +1635,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,8 +1673,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1633,24 +1711,27 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45473</v>
       </c>
       <c r="G38" s="2">
         <v>45382</v>
@@ -1665,16 +1746,19 @@
         <v>45107</v>
       </c>
       <c r="K38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,22 +1788,23 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E41" s="3">
         <v>289900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>312300</v>
       </c>
-      <c r="F41" s="3">
-        <v>279400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>281400</v>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H41" s="3">
         <v>165500</v>
@@ -1730,16 +1816,19 @@
         <v>153600</v>
       </c>
       <c r="K41" s="3">
+        <v>153600</v>
+      </c>
+      <c r="L41" s="3">
         <v>160400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,22 +1862,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1036600</v>
+      </c>
+      <c r="E43" s="3">
         <v>893700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>962700</v>
       </c>
-      <c r="F43" s="3">
-        <v>885600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>891700</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>644600</v>
@@ -1800,30 +1892,33 @@
         <v>630400</v>
       </c>
       <c r="K43" s="3">
+        <v>630400</v>
+      </c>
+      <c r="L43" s="3">
         <v>664400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>595300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>789300</v>
+      </c>
+      <c r="E44" s="3">
         <v>746000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>803700</v>
       </c>
-      <c r="F44" s="3">
-        <v>736500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>741600</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3">
         <v>537900</v>
@@ -1835,30 +1930,33 @@
         <v>580700</v>
       </c>
       <c r="K44" s="3">
+        <v>580700</v>
+      </c>
+      <c r="L44" s="3">
         <v>561600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>546400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E45" s="3">
         <v>16200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17400</v>
       </c>
-      <c r="F45" s="3">
-        <v>35300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>35500</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
         <v>55200</v>
@@ -1870,30 +1968,33 @@
         <v>9200</v>
       </c>
       <c r="K45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L45" s="3">
         <v>12300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2103200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1945800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2096100</v>
       </c>
-      <c r="F46" s="3">
-        <v>1936800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1950200</v>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H46" s="3">
         <v>1403200</v>
@@ -1905,30 +2006,33 @@
         <v>1374000</v>
       </c>
       <c r="K46" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="L46" s="3">
         <v>1398700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1327700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E47" s="3">
         <v>24800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26800</v>
       </c>
-      <c r="F47" s="3">
-        <v>27500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>27700</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>30400</v>
@@ -1940,30 +2044,33 @@
         <v>32100</v>
       </c>
       <c r="K47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="L47" s="3">
         <v>31800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3150800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3073100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3310600</v>
       </c>
-      <c r="F48" s="3">
-        <v>3071100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3092400</v>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H48" s="3">
         <v>1827800</v>
@@ -1975,30 +2082,33 @@
         <v>1808000</v>
       </c>
       <c r="K48" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="L48" s="3">
         <v>1770200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1734800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10675700</v>
+      </c>
+      <c r="E49" s="3">
         <v>10378100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11180200</v>
       </c>
-      <c r="F49" s="3">
-        <v>10996800</v>
-      </c>
       <c r="G49" s="3">
-        <v>11072700</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>672100</v>
@@ -2010,16 +2120,19 @@
         <v>669000</v>
       </c>
       <c r="K49" s="3">
+        <v>669000</v>
+      </c>
+      <c r="L49" s="3">
         <v>670700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>675000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,22 +2204,25 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E52" s="3">
         <v>25600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27500</v>
       </c>
-      <c r="F52" s="3">
-        <v>37000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>37200</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
         <v>15600</v>
@@ -2118,13 +2237,16 @@
         <v>17400</v>
       </c>
       <c r="L52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="M52" s="3">
         <v>17800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,22 +2280,25 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16274800</v>
+      </c>
+      <c r="E54" s="3">
         <v>15732100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16948000</v>
       </c>
-      <c r="F54" s="3">
-        <v>16342200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>16455100</v>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H54" s="3">
         <v>4210300</v>
@@ -2185,16 +2310,19 @@
         <v>4137600</v>
       </c>
       <c r="K54" s="3">
+        <v>4137600</v>
+      </c>
+      <c r="L54" s="3">
         <v>4124800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4020600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,22 +2352,23 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E57" s="3">
         <v>438000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>471900</v>
       </c>
-      <c r="F57" s="3">
-        <v>370500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>373100</v>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H57" s="3">
         <v>239600</v>
@@ -2250,30 +2380,33 @@
         <v>193600</v>
       </c>
       <c r="K57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="L57" s="3">
         <v>211800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>268500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>464700</v>
+      </c>
+      <c r="E58" s="3">
         <v>275800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>297100</v>
       </c>
-      <c r="F58" s="3">
-        <v>982200</v>
-      </c>
       <c r="G58" s="3">
-        <v>989000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>477500</v>
@@ -2285,30 +2418,33 @@
         <v>480800</v>
       </c>
       <c r="K58" s="3">
+        <v>480800</v>
+      </c>
+      <c r="L58" s="3">
         <v>485300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>437100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E59" s="3">
         <v>412900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>444800</v>
       </c>
-      <c r="F59" s="3">
-        <v>394400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>397100</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
         <v>238200</v>
@@ -2320,30 +2456,33 @@
         <v>327600</v>
       </c>
       <c r="K59" s="3">
+        <v>327600</v>
+      </c>
+      <c r="L59" s="3">
         <v>340700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>195300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1264800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1126700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1213800</v>
       </c>
-      <c r="F60" s="3">
-        <v>1747100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1759200</v>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
         <v>1076900</v>
@@ -2355,30 +2494,33 @@
         <v>1002000</v>
       </c>
       <c r="K60" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="L60" s="3">
         <v>1037800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1000400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1371700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1584400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1706900</v>
       </c>
-      <c r="F61" s="3">
-        <v>1149100</v>
-      </c>
       <c r="G61" s="3">
-        <v>1157100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>676400</v>
@@ -2390,30 +2532,33 @@
         <v>710200</v>
       </c>
       <c r="K61" s="3">
+        <v>710200</v>
+      </c>
+      <c r="L61" s="3">
         <v>722000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>561400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E62" s="3">
         <v>41100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44300</v>
       </c>
-      <c r="F62" s="3">
-        <v>23400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>23500</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>14800</v>
@@ -2425,16 +2570,19 @@
         <v>133100</v>
       </c>
       <c r="K62" s="3">
+        <v>133100</v>
+      </c>
+      <c r="L62" s="3">
         <v>162200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>158500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,22 +2692,25 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4136100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4161500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4483200</v>
       </c>
-      <c r="F66" s="3">
-        <v>4550700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>4582200</v>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H66" s="3">
         <v>2082100</v>
@@ -2565,16 +2722,19 @@
         <v>2115000</v>
       </c>
       <c r="K66" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="L66" s="3">
         <v>2187300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1976300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,22 +2898,25 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12110100</v>
+      </c>
+      <c r="E72" s="3">
         <v>11421900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12304700</v>
       </c>
-      <c r="F72" s="3">
-        <v>11678700</v>
-      </c>
-      <c r="G72" s="3">
-        <v>11759300</v>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H72" s="3">
         <v>2039800</v>
@@ -2755,16 +2928,19 @@
         <v>1890900</v>
       </c>
       <c r="K72" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="L72" s="3">
         <v>1791200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1876700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,22 +3050,25 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12138700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11570600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12464900</v>
       </c>
-      <c r="F76" s="3">
-        <v>11789900</v>
-      </c>
       <c r="G76" s="3">
-        <v>11871300</v>
+        <v>2023500</v>
       </c>
       <c r="H76" s="3">
         <v>2072900</v>
@@ -2895,16 +3080,19 @@
         <v>1962100</v>
       </c>
       <c r="K76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="L76" s="3">
         <v>1878200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1988100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,24 +3126,27 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45473</v>
       </c>
       <c r="G80" s="2">
         <v>45382</v>
@@ -2970,16 +3161,19 @@
         <v>45107</v>
       </c>
       <c r="K80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3013,8 +3207,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,8 +3225,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3054,17 +3252,20 @@
       <c r="J83" s="3">
         <v>53000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>158500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,22 +3451,25 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E89" s="3">
         <v>254600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>274300</v>
       </c>
-      <c r="F89" s="3">
-        <v>282900</v>
-      </c>
       <c r="G89" s="3">
-        <v>284900</v>
+        <v>190400</v>
       </c>
       <c r="H89" s="3">
         <v>166400</v>
@@ -3265,16 +3481,19 @@
         <v>165700</v>
       </c>
       <c r="K89" s="3">
+        <v>165700</v>
+      </c>
+      <c r="L89" s="3">
         <v>45800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>83900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,22 +3507,23 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-105100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-113300</v>
       </c>
-      <c r="F91" s="3">
-        <v>-72400</v>
-      </c>
       <c r="G91" s="3">
-        <v>-72900</v>
+        <v>-49100</v>
       </c>
       <c r="H91" s="3">
         <v>-72400</v>
@@ -3315,16 +3535,19 @@
         <v>-75400</v>
       </c>
       <c r="K91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-60500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-119300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,22 +3619,25 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-80700</v>
       </c>
-      <c r="F94" s="3">
-        <v>-29400</v>
-      </c>
       <c r="G94" s="3">
-        <v>-29600</v>
+        <v>-32900</v>
       </c>
       <c r="H94" s="3">
         <v>-89400</v>
@@ -3420,16 +3649,19 @@
         <v>-103300</v>
       </c>
       <c r="K94" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="L94" s="3">
         <v>-49400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-129000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,22 +3675,23 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>64600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>69600</v>
       </c>
-      <c r="F96" s="3">
-        <v>66900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>67400</v>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H96" s="3">
         <v>172500</v>
@@ -3470,16 +3703,19 @@
         <v>100</v>
       </c>
       <c r="K96" s="3">
+        <v>100</v>
+      </c>
+      <c r="L96" s="3">
         <v>242400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,22 +3825,25 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-110400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-170700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-183900</v>
       </c>
-      <c r="F100" s="3">
-        <v>-200000</v>
-      </c>
       <c r="G100" s="3">
-        <v>-201400</v>
+        <v>-97000</v>
       </c>
       <c r="H100" s="3">
         <v>-82300</v>
@@ -3610,16 +3855,19 @@
         <v>-66800</v>
       </c>
       <c r="K100" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="L100" s="3">
         <v>14400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3645,30 +3893,33 @@
         <v>3100</v>
       </c>
       <c r="K101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>9300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10700</v>
       </c>
-      <c r="F102" s="3">
-        <v>59500</v>
-      </c>
       <c r="G102" s="3">
-        <v>59900</v>
+        <v>68100</v>
       </c>
       <c r="H102" s="3">
         <v>-8700</v>
@@ -3680,12 +3931,15 @@
         <v>-7600</v>
       </c>
       <c r="K102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="L102" s="3">
         <v>8600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -656,71 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45107</v>
       </c>
       <c r="K7" s="2">
         <v>45107</v>
       </c>
       <c r="L7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +762,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +803,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +984,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,8 +1025,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,8 +1041,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1052,8 +1080,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1090,8 +1121,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1144,8 +1179,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1182,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,8 +1261,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1258,8 +1302,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1343,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,8 +1384,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1372,8 +1425,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1410,8 +1466,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1548,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1600,8 +1671,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1638,8 +1712,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,8 +1753,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1714,51 +1794,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45107</v>
       </c>
       <c r="K38" s="2">
         <v>45107</v>
       </c>
       <c r="L38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>385400</v>
+      </c>
+      <c r="E41" s="3">
         <v>269700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>289900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>312300</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>165500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>166700</v>
-      </c>
-      <c r="J41" s="3">
-        <v>153600</v>
       </c>
       <c r="K41" s="3">
         <v>153600</v>
       </c>
       <c r="L41" s="3">
+        <v>153600</v>
+      </c>
+      <c r="M41" s="3">
         <v>160400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1865,274 +1956,298 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1041600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1036600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>893700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>962700</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>644600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>620100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>630400</v>
       </c>
       <c r="K43" s="3">
         <v>630400</v>
       </c>
       <c r="L43" s="3">
+        <v>630400</v>
+      </c>
+      <c r="M43" s="3">
         <v>664400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>595300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>939000</v>
+      </c>
+      <c r="E44" s="3">
         <v>789300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>746000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>803700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>537900</v>
-      </c>
-      <c r="I44" s="3">
-        <v>550000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>580700</v>
       </c>
       <c r="K44" s="3">
         <v>580700</v>
       </c>
       <c r="L44" s="3">
+        <v>580700</v>
+      </c>
+      <c r="M44" s="3">
         <v>561600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>546400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>17400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>55200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>9200</v>
       </c>
       <c r="K45" s="3">
         <v>9200</v>
       </c>
       <c r="L45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M45" s="3">
         <v>12300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2409700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2103200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1945800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2096100</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>1403200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1339100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1374000</v>
       </c>
       <c r="K46" s="3">
         <v>1374000</v>
       </c>
       <c r="L46" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="M46" s="3">
         <v>1398700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1327700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E47" s="3">
         <v>24500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26800</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>30400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>29900</v>
-      </c>
-      <c r="J47" s="3">
-        <v>32100</v>
       </c>
       <c r="K47" s="3">
         <v>32100</v>
       </c>
       <c r="L47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="M47" s="3">
         <v>31800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3328400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3150800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3073100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3310600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>1827800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1798400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1808000</v>
       </c>
       <c r="K48" s="3">
         <v>1808000</v>
       </c>
       <c r="L48" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="M48" s="3">
         <v>1770200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1734800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13161700</v>
+      </c>
+      <c r="E49" s="3">
         <v>10675700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10378100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11180200</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>672100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>647100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>669000</v>
       </c>
       <c r="K49" s="3">
         <v>669000</v>
       </c>
       <c r="L49" s="3">
+        <v>669000</v>
+      </c>
+      <c r="M49" s="3">
         <v>670700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>675000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,31 +2325,34 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E52" s="3">
         <v>26200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27500</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>15600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>17600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>17400</v>
       </c>
       <c r="K52" s="3">
         <v>17400</v>
@@ -2240,13 +2361,16 @@
         <v>17400</v>
       </c>
       <c r="M52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="N52" s="3">
         <v>17800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19261400</v>
+      </c>
+      <c r="E54" s="3">
         <v>16274800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15732100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16948000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>4210300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>4047700</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4137600</v>
       </c>
       <c r="K54" s="3">
         <v>4137600</v>
       </c>
       <c r="L54" s="3">
+        <v>4137600</v>
+      </c>
+      <c r="M54" s="3">
         <v>4124800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4020600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,236 +2484,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>354800</v>
+      </c>
+      <c r="E57" s="3">
         <v>343300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>438000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>471900</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>239600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>207100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>193600</v>
       </c>
       <c r="K57" s="3">
         <v>193600</v>
       </c>
       <c r="L57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="M57" s="3">
         <v>211800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>268500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>407500</v>
+      </c>
+      <c r="E58" s="3">
         <v>464700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>275800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>297100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>477500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>350900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>480800</v>
       </c>
       <c r="K58" s="3">
         <v>480800</v>
       </c>
       <c r="L58" s="3">
+        <v>480800</v>
+      </c>
+      <c r="M58" s="3">
         <v>485300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>437100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E59" s="3">
         <v>456900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>412900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>444800</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>238200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>324700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>327600</v>
       </c>
       <c r="K59" s="3">
         <v>327600</v>
       </c>
       <c r="L59" s="3">
+        <v>327600</v>
+      </c>
+      <c r="M59" s="3">
         <v>340700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>195300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1375300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1264800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1126700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1213800</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>1076900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>882700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1002000</v>
       </c>
       <c r="K60" s="3">
         <v>1002000</v>
       </c>
       <c r="L60" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="M60" s="3">
         <v>1037800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1000400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3493500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1371700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1584400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1706900</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>676400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>663800</v>
-      </c>
-      <c r="J61" s="3">
-        <v>710200</v>
       </c>
       <c r="K61" s="3">
         <v>710200</v>
       </c>
       <c r="L61" s="3">
+        <v>710200</v>
+      </c>
+      <c r="M61" s="3">
         <v>722000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>561400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E62" s="3">
         <v>45800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>41100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44300</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>14800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>134200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>133100</v>
       </c>
       <c r="K62" s="3">
         <v>133100</v>
       </c>
       <c r="L62" s="3">
+        <v>133100</v>
+      </c>
+      <c r="M62" s="3">
         <v>162200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>158500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6645000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4136100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4161500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4483200</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>2082100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1935800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2115000</v>
       </c>
       <c r="K66" s="3">
         <v>2115000</v>
       </c>
       <c r="L66" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="M66" s="3">
         <v>2187300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1976300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>12110100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11421900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12304700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>2039800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>1959200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>1890900</v>
       </c>
       <c r="K72" s="3">
         <v>1890900</v>
       </c>
       <c r="L72" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="M72" s="3">
         <v>1791200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1876700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12616400</v>
+      </c>
+      <c r="E76" s="3">
         <v>12138700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11570600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12464900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
         <v>2023500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2072900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>2054400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1962100</v>
       </c>
       <c r="K76" s="3">
         <v>1962100</v>
       </c>
       <c r="L76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="M76" s="3">
         <v>1878200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1988100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,51 +3319,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45107</v>
       </c>
       <c r="K80" s="2">
         <v>45107</v>
       </c>
       <c r="L80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3210,8 +3406,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
+        <v>68300</v>
+      </c>
+      <c r="F83" s="3">
         <v>9600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>47100</v>
       </c>
-      <c r="F83" s="3">
-        <v>-52300</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I83" s="3">
         <v>52100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>154900</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
-        <v>53000</v>
       </c>
       <c r="K83" s="3">
         <v>53000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>158500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>375900</v>
+      </c>
+      <c r="E89" s="3">
         <v>115000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>254600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>274300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3">
         <v>190400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>166400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>225000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>165700</v>
       </c>
       <c r="K89" s="3">
         <v>165700</v>
       </c>
       <c r="L89" s="3">
+        <v>165700</v>
+      </c>
+      <c r="M89" s="3">
         <v>45800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-105100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-113300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-49100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-72400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-62000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-75400</v>
       </c>
       <c r="K91" s="3">
         <v>-75400</v>
       </c>
       <c r="L91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-60500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-119300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1810200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-75000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
         <v>-32900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-89400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-68900</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-103300</v>
       </c>
       <c r="K94" s="3">
         <v>-103300</v>
       </c>
       <c r="L94" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="M94" s="3">
         <v>-49400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-129000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>308200</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>64600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>69600</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>172500</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
-        <v>100</v>
       </c>
       <c r="K96" s="3">
         <v>100</v>
       </c>
       <c r="L96" s="3">
+        <v>100</v>
+      </c>
+      <c r="M96" s="3">
         <v>242400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,118 +4072,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1537800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-110400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-170700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-183900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
         <v>-97000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-82300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-138600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-66800</v>
       </c>
       <c r="K100" s="3">
         <v>-66800</v>
       </c>
       <c r="L100" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="M100" s="3">
         <v>14400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-6500</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3100</v>
       </c>
       <c r="K101" s="3">
         <v>3100</v>
       </c>
       <c r="L101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>9300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>68100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-8700</v>
-      </c>
-      <c r="I102" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-7600</v>
       </c>
       <c r="K102" s="3">
         <v>-7600</v>
       </c>
       <c r="L102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="M102" s="3">
         <v>8600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-48300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -656,80 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45291</v>
       </c>
       <c r="K7" s="2">
         <v>45291</v>
       </c>
       <c r="L7" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="M7" s="2">
         <v>45107</v>
       </c>
       <c r="N7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +774,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1028,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1075,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1093,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,8 +1138,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1206,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1251,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,8 +1345,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1351,8 +1392,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1439,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1486,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1483,8 +1533,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1674,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1768,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,8 +1815,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1909,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1879,57 +1956,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45291</v>
       </c>
       <c r="K38" s="2">
         <v>45291</v>
       </c>
       <c r="L38" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="M38" s="2">
         <v>45107</v>
       </c>
       <c r="N38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2048,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>323200</v>
+      </c>
+      <c r="E41" s="3">
         <v>330000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>385400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>269700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H41" s="3">
+        <v>289900</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>279400</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
-        <v>165500</v>
       </c>
       <c r="K41" s="3">
         <v>165500</v>
       </c>
       <c r="L41" s="3">
-        <v>153600</v>
+        <v>165500</v>
       </c>
       <c r="M41" s="3">
         <v>153600</v>
       </c>
       <c r="N41" s="3">
+        <v>153600</v>
+      </c>
+      <c r="O41" s="3">
         <v>160400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>149600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,316 +2140,340 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1074800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1061500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1041600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1036600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3">
+        <v>893700</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>885600</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
-        <v>644600</v>
       </c>
       <c r="K43" s="3">
         <v>644600</v>
       </c>
       <c r="L43" s="3">
-        <v>630400</v>
+        <v>644600</v>
       </c>
       <c r="M43" s="3">
         <v>630400</v>
       </c>
       <c r="N43" s="3">
+        <v>630400</v>
+      </c>
+      <c r="O43" s="3">
         <v>664400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>595300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>906700</v>
+      </c>
+      <c r="E44" s="3">
         <v>870600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>939000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>789300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3">
+        <v>746000</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>736500</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
-        <v>537900</v>
       </c>
       <c r="K44" s="3">
         <v>537900</v>
       </c>
       <c r="L44" s="3">
-        <v>580700</v>
+        <v>537900</v>
       </c>
       <c r="M44" s="3">
         <v>580700</v>
       </c>
       <c r="N44" s="3">
+        <v>580700</v>
+      </c>
+      <c r="O44" s="3">
         <v>561600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>546400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E45" s="3">
         <v>33100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>35300</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
-        <v>55200</v>
       </c>
       <c r="K45" s="3">
         <v>55200</v>
       </c>
       <c r="L45" s="3">
-        <v>9200</v>
+        <v>55200</v>
       </c>
       <c r="M45" s="3">
         <v>9200</v>
       </c>
       <c r="N45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="O45" s="3">
         <v>12300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2328500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2295200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2409700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2103200</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H46" s="3">
+        <v>1945800</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>1936800</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1403200</v>
       </c>
       <c r="K46" s="3">
         <v>1403200</v>
       </c>
       <c r="L46" s="3">
-        <v>1374000</v>
+        <v>1403200</v>
       </c>
       <c r="M46" s="3">
         <v>1374000</v>
       </c>
       <c r="N46" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="O46" s="3">
         <v>1398700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1327700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E47" s="3">
         <v>24200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>23700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>24500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H47" s="3">
+        <v>24800</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>27500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
-        <v>30400</v>
       </c>
       <c r="K47" s="3">
         <v>30400</v>
       </c>
       <c r="L47" s="3">
-        <v>32100</v>
+        <v>30400</v>
       </c>
       <c r="M47" s="3">
         <v>32100</v>
       </c>
       <c r="N47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="O47" s="3">
         <v>31800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3520400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3366200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3328400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3150800</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3">
+        <v>3073100</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>3071100</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1827800</v>
       </c>
       <c r="K48" s="3">
         <v>1827800</v>
       </c>
       <c r="L48" s="3">
-        <v>1808000</v>
+        <v>1827800</v>
       </c>
       <c r="M48" s="3">
         <v>1808000</v>
       </c>
       <c r="N48" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="O48" s="3">
         <v>1770200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1734800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13019100</v>
+      </c>
+      <c r="E49" s="3">
         <v>13108900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13161700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10675700</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>10378100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>10996800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>672100</v>
       </c>
       <c r="K49" s="3">
         <v>672100</v>
       </c>
       <c r="L49" s="3">
-        <v>669000</v>
+        <v>672100</v>
       </c>
       <c r="M49" s="3">
         <v>669000</v>
       </c>
       <c r="N49" s="3">
+        <v>669000</v>
+      </c>
+      <c r="O49" s="3">
         <v>670700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>675000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,37 +2563,40 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E52" s="3">
         <v>21600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>37000</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15600</v>
       </c>
       <c r="K52" s="3">
         <v>15600</v>
       </c>
       <c r="L52" s="3">
-        <v>17400</v>
+        <v>15600</v>
       </c>
       <c r="M52" s="3">
         <v>17400</v>
@@ -2487,13 +2605,16 @@
         <v>17400</v>
       </c>
       <c r="O52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="P52" s="3">
         <v>17800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2657,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19195800</v>
+      </c>
+      <c r="E54" s="3">
         <v>19127800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19261400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16274800</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H54" s="3">
+        <v>15732100</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>16342200</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4210300</v>
       </c>
       <c r="K54" s="3">
         <v>4210300</v>
       </c>
       <c r="L54" s="3">
-        <v>4137600</v>
+        <v>4210300</v>
       </c>
       <c r="M54" s="3">
         <v>4137600</v>
       </c>
       <c r="N54" s="3">
+        <v>4137600</v>
+      </c>
+      <c r="O54" s="3">
         <v>4124800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4020600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2744,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>494100</v>
+      </c>
+      <c r="E57" s="3">
         <v>349900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>354800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>343300</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3">
+        <v>438000</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>370500</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
-        <v>239600</v>
       </c>
       <c r="K57" s="3">
         <v>239600</v>
       </c>
       <c r="L57" s="3">
-        <v>193600</v>
+        <v>239600</v>
       </c>
       <c r="M57" s="3">
         <v>193600</v>
       </c>
       <c r="N57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="O57" s="3">
         <v>211800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>268500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1997800</v>
+      </c>
+      <c r="E58" s="3">
         <v>355500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>407500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>464700</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>275800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>982200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>477500</v>
       </c>
       <c r="K58" s="3">
         <v>477500</v>
       </c>
       <c r="L58" s="3">
-        <v>480800</v>
+        <v>477500</v>
       </c>
       <c r="M58" s="3">
         <v>480800</v>
       </c>
       <c r="N58" s="3">
+        <v>480800</v>
+      </c>
+      <c r="O58" s="3">
         <v>485300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>437100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>726800</v>
+      </c>
+      <c r="E59" s="3">
         <v>716600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>613000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>456900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H59" s="3">
+        <v>412900</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>394400</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
-        <v>238200</v>
       </c>
       <c r="K59" s="3">
         <v>238200</v>
       </c>
       <c r="L59" s="3">
-        <v>327600</v>
+        <v>238200</v>
       </c>
       <c r="M59" s="3">
         <v>327600</v>
       </c>
       <c r="N59" s="3">
+        <v>327600</v>
+      </c>
+      <c r="O59" s="3">
         <v>340700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>195300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3218600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1422000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1375300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1264800</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H60" s="3">
+        <v>1126700</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>1747100</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1076900</v>
       </c>
       <c r="K60" s="3">
         <v>1076900</v>
       </c>
       <c r="L60" s="3">
-        <v>1002000</v>
+        <v>1076900</v>
       </c>
       <c r="M60" s="3">
         <v>1002000</v>
       </c>
       <c r="N60" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="O60" s="3">
         <v>1037800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1000400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1530900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3290600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3493500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1371700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>1584400</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1149100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>676400</v>
       </c>
       <c r="K61" s="3">
         <v>676400</v>
       </c>
       <c r="L61" s="3">
-        <v>710200</v>
+        <v>676400</v>
       </c>
       <c r="M61" s="3">
         <v>710200</v>
       </c>
       <c r="N61" s="3">
+        <v>710200</v>
+      </c>
+      <c r="O61" s="3">
         <v>722000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>561400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E62" s="3">
         <v>73000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>68600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>45800</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H62" s="3">
+        <v>41100</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>23400</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
-        <v>14800</v>
       </c>
       <c r="K62" s="3">
         <v>14800</v>
       </c>
       <c r="L62" s="3">
-        <v>133100</v>
+        <v>14800</v>
       </c>
       <c r="M62" s="3">
         <v>133100</v>
       </c>
       <c r="N62" s="3">
+        <v>133100</v>
+      </c>
+      <c r="O62" s="3">
         <v>162200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>158500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3165,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6450500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6521800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6645000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4136100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H66" s="3">
+        <v>4161500</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>4550700</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2082100</v>
       </c>
       <c r="K66" s="3">
         <v>2082100</v>
       </c>
       <c r="L66" s="3">
-        <v>2115000</v>
+        <v>2082100</v>
       </c>
       <c r="M66" s="3">
         <v>2115000</v>
       </c>
       <c r="N66" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="O66" s="3">
         <v>2187300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1976300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3419,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
+      <c r="D72" s="3">
+        <v>13101400</v>
       </c>
       <c r="E72" s="3">
+        <v>12951700</v>
+      </c>
+      <c r="F72" s="3">
         <v>12961500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12110100</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3">
+        <v>11421900</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>11678700</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
-        <v>2039800</v>
       </c>
       <c r="K72" s="3">
         <v>2039800</v>
       </c>
       <c r="L72" s="3">
-        <v>1890900</v>
+        <v>2039800</v>
       </c>
       <c r="M72" s="3">
         <v>1890900</v>
       </c>
       <c r="N72" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="O72" s="3">
         <v>1791200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1876700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3607,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12745300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12606000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12616400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12138700</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H76" s="3">
+        <v>11570600</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>11789900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>2023500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>2072900</v>
       </c>
       <c r="K76" s="3">
         <v>2072900</v>
       </c>
       <c r="L76" s="3">
-        <v>1962100</v>
+        <v>2072900</v>
       </c>
       <c r="M76" s="3">
         <v>1962100</v>
       </c>
       <c r="N76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="O76" s="3">
         <v>1878200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1988100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3701,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45291</v>
       </c>
       <c r="K80" s="2">
         <v>45291</v>
       </c>
       <c r="L80" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="M80" s="2">
         <v>45107</v>
       </c>
       <c r="N80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3607,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3821,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>66900</v>
+      </c>
+      <c r="F83" s="3">
         <v>64400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>68300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>47100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>25700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>52100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>154900</v>
       </c>
       <c r="K83" s="3">
         <v>154900</v>
       </c>
       <c r="L83" s="3">
-        <v>53000</v>
+        <v>154900</v>
       </c>
       <c r="M83" s="3">
         <v>53000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="N83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>158500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4101,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>385300</v>
+      </c>
+      <c r="E89" s="3">
         <v>547700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>375900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>115000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>237300</v>
+      </c>
+      <c r="I89" s="3">
         <v>292900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>376700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>190400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>166400</v>
       </c>
       <c r="K89" s="3">
         <v>166400</v>
       </c>
       <c r="L89" s="3">
-        <v>165700</v>
+        <v>166400</v>
       </c>
       <c r="M89" s="3">
         <v>165700</v>
       </c>
       <c r="N89" s="3">
+        <v>165700</v>
+      </c>
+      <c r="O89" s="3">
         <v>45800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>83900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4169,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-230700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-111800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-131300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-85100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-96100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-49100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-72400</v>
       </c>
       <c r="K91" s="3">
         <v>-72400</v>
       </c>
       <c r="L91" s="3">
-        <v>-75400</v>
+        <v>-72400</v>
       </c>
       <c r="M91" s="3">
         <v>-75400</v>
       </c>
       <c r="N91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-60500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-119300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4308,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-265600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-193600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1810200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-101700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-52000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-26100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-32900</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-89400</v>
       </c>
       <c r="K94" s="3">
         <v>-89400</v>
       </c>
       <c r="L94" s="3">
-        <v>-103300</v>
+        <v>-89400</v>
       </c>
       <c r="M94" s="3">
         <v>-103300</v>
       </c>
       <c r="N94" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="O94" s="3">
         <v>-49400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-129000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4376,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>164600</v>
+      </c>
+      <c r="F96" s="3">
         <v>308200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>139300</v>
+      </c>
+      <c r="J96" s="3">
         <v>133800</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
-        <v>172500</v>
       </c>
       <c r="K96" s="3">
         <v>172500</v>
       </c>
       <c r="L96" s="3">
-        <v>100</v>
+        <v>172500</v>
       </c>
       <c r="M96" s="3">
         <v>100</v>
       </c>
       <c r="N96" s="3">
+        <v>100</v>
+      </c>
+      <c r="O96" s="3">
         <v>242400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4562,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-119900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-412900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1537800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-110400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-125100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-233100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-303800</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-97000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-82300</v>
       </c>
       <c r="K100" s="3">
         <v>-82300</v>
       </c>
       <c r="L100" s="3">
-        <v>-66800</v>
+        <v>-82300</v>
       </c>
       <c r="M100" s="3">
         <v>-66800</v>
       </c>
       <c r="N100" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="O100" s="3">
         <v>14400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F101" s="3">
         <v>4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>7600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-3200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-6500</v>
       </c>
       <c r="K101" s="3">
         <v>-6500</v>
       </c>
       <c r="L101" s="3">
-        <v>3100</v>
+        <v>-6500</v>
       </c>
       <c r="M101" s="3">
         <v>3100</v>
       </c>
       <c r="N101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>9300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-55000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>92400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I102" s="3">
         <v>13700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>51400</v>
-      </c>
-      <c r="I102" s="3">
-        <v>68100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-8700</v>
       </c>
       <c r="K102" s="3">
         <v>-8700</v>
       </c>
       <c r="L102" s="3">
-        <v>-7600</v>
+        <v>-8700</v>
       </c>
       <c r="M102" s="3">
         <v>-7600</v>
       </c>
       <c r="N102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O102" s="3">
         <v>8600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -656,82 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45291</v>
       </c>
       <c r="L7" s="2">
         <v>45291</v>
       </c>
       <c r="M7" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="N7" s="2">
         <v>45107</v>
       </c>
       <c r="O7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -777,8 +781,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +903,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,8 +1001,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,8 +1120,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1141,8 +1168,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1188,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1240,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1254,8 +1288,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,8 +1338,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,8 +1388,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1395,8 +1438,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,8 +1538,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1536,8 +1588,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,8 +1638,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1838,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1818,8 +1888,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1865,8 +1938,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,8 +1988,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1959,60 +2038,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45291</v>
       </c>
       <c r="L38" s="2">
         <v>45291</v>
       </c>
       <c r="M38" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="N38" s="2">
         <v>45107</v>
       </c>
       <c r="O38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,55 +2135,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>377300</v>
+      </c>
+      <c r="E41" s="3">
         <v>323200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>330000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>385400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>269700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>289900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>279400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>165500</v>
       </c>
       <c r="L41" s="3">
         <v>165500</v>
       </c>
       <c r="M41" s="3">
-        <v>153600</v>
+        <v>165500</v>
       </c>
       <c r="N41" s="3">
         <v>153600</v>
       </c>
       <c r="O41" s="3">
+        <v>153600</v>
+      </c>
+      <c r="P41" s="3">
         <v>160400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>149600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,337 +2233,361 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1064900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1074800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1061500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1041600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1036600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>893700</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>885600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>644600</v>
       </c>
       <c r="L43" s="3">
         <v>644600</v>
       </c>
       <c r="M43" s="3">
-        <v>630400</v>
+        <v>644600</v>
       </c>
       <c r="N43" s="3">
         <v>630400</v>
       </c>
       <c r="O43" s="3">
+        <v>630400</v>
+      </c>
+      <c r="P43" s="3">
         <v>664400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>595300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>914000</v>
+      </c>
+      <c r="E44" s="3">
         <v>906700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>870600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>939000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>789300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>746000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>736500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>537900</v>
       </c>
       <c r="L44" s="3">
         <v>537900</v>
       </c>
       <c r="M44" s="3">
-        <v>580700</v>
+        <v>537900</v>
       </c>
       <c r="N44" s="3">
         <v>580700</v>
       </c>
       <c r="O44" s="3">
+        <v>580700</v>
+      </c>
+      <c r="P44" s="3">
         <v>561600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>546400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3">
         <v>23800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>16200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>35300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>55200</v>
       </c>
       <c r="L45" s="3">
         <v>55200</v>
       </c>
       <c r="M45" s="3">
-        <v>9200</v>
+        <v>55200</v>
       </c>
       <c r="N45" s="3">
         <v>9200</v>
       </c>
       <c r="O45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P45" s="3">
         <v>12300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2358700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2328500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2295200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2409700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2103200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1945800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>1936800</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1403200</v>
       </c>
       <c r="L46" s="3">
         <v>1403200</v>
       </c>
       <c r="M46" s="3">
-        <v>1374000</v>
+        <v>1403200</v>
       </c>
       <c r="N46" s="3">
         <v>1374000</v>
       </c>
       <c r="O46" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="P46" s="3">
         <v>1398700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1327700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E47" s="3">
         <v>20500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>23700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>24500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24800</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>27500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>30400</v>
       </c>
       <c r="L47" s="3">
         <v>30400</v>
       </c>
       <c r="M47" s="3">
-        <v>32100</v>
+        <v>30400</v>
       </c>
       <c r="N47" s="3">
         <v>32100</v>
       </c>
       <c r="O47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="P47" s="3">
         <v>31800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>32000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3522700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3520400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3366200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3328400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3150800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3073100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>3071100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1827800</v>
       </c>
       <c r="L48" s="3">
         <v>1827800</v>
       </c>
       <c r="M48" s="3">
-        <v>1808000</v>
+        <v>1827800</v>
       </c>
       <c r="N48" s="3">
         <v>1808000</v>
       </c>
       <c r="O48" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="P48" s="3">
         <v>1770200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1734800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12843300</v>
+      </c>
+      <c r="E49" s="3">
         <v>13019100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13108900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13161700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10675700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10378100</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>10996800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>672100</v>
       </c>
       <c r="L49" s="3">
         <v>672100</v>
       </c>
       <c r="M49" s="3">
-        <v>669000</v>
+        <v>672100</v>
       </c>
       <c r="N49" s="3">
         <v>669000</v>
       </c>
       <c r="O49" s="3">
+        <v>669000</v>
+      </c>
+      <c r="P49" s="3">
         <v>670700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>675000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,40 +2683,43 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E52" s="3">
         <v>22900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25600</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>37000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>15600</v>
       </c>
       <c r="L52" s="3">
         <v>15600</v>
       </c>
       <c r="M52" s="3">
-        <v>17400</v>
+        <v>15600</v>
       </c>
       <c r="N52" s="3">
         <v>17400</v>
@@ -2608,13 +2728,16 @@
         <v>17400</v>
       </c>
       <c r="P52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>17800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,55 +2783,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19051400</v>
+      </c>
+      <c r="E54" s="3">
         <v>19195800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19127800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19261400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16274800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15732100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>16342200</v>
-      </c>
-      <c r="K54" s="3">
-        <v>4210300</v>
       </c>
       <c r="L54" s="3">
         <v>4210300</v>
       </c>
       <c r="M54" s="3">
-        <v>4137600</v>
+        <v>4210300</v>
       </c>
       <c r="N54" s="3">
         <v>4137600</v>
       </c>
       <c r="O54" s="3">
+        <v>4137600</v>
+      </c>
+      <c r="P54" s="3">
         <v>4124800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4020600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,290 +2875,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>419500</v>
+      </c>
+      <c r="E57" s="3">
         <v>494100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>349900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>354800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>343300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>438000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>370500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>239600</v>
       </c>
       <c r="L57" s="3">
         <v>239600</v>
       </c>
       <c r="M57" s="3">
-        <v>193600</v>
+        <v>239600</v>
       </c>
       <c r="N57" s="3">
         <v>193600</v>
       </c>
       <c r="O57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="P57" s="3">
         <v>211800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>268500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>333300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1997800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>355500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>407500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>464700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>275800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>982200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>477500</v>
       </c>
       <c r="L58" s="3">
         <v>477500</v>
       </c>
       <c r="M58" s="3">
-        <v>480800</v>
+        <v>477500</v>
       </c>
       <c r="N58" s="3">
         <v>480800</v>
       </c>
       <c r="O58" s="3">
+        <v>480800</v>
+      </c>
+      <c r="P58" s="3">
         <v>485300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>437100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>656600</v>
+      </c>
+      <c r="E59" s="3">
         <v>726800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>716600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>613000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>456900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>412900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>394400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>238200</v>
       </c>
       <c r="L59" s="3">
         <v>238200</v>
       </c>
       <c r="M59" s="3">
-        <v>327600</v>
+        <v>238200</v>
       </c>
       <c r="N59" s="3">
         <v>327600</v>
       </c>
       <c r="O59" s="3">
+        <v>327600</v>
+      </c>
+      <c r="P59" s="3">
         <v>340700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>195300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1409400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3218600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1422000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1375300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1264800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1126700</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>1747100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1076900</v>
       </c>
       <c r="L60" s="3">
         <v>1076900</v>
       </c>
       <c r="M60" s="3">
-        <v>1002000</v>
+        <v>1076900</v>
       </c>
       <c r="N60" s="3">
         <v>1002000</v>
       </c>
       <c r="O60" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="P60" s="3">
         <v>1037800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1000400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3370500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1530900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3290600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3493500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1371700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1584400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1149100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>676400</v>
       </c>
       <c r="L61" s="3">
         <v>676400</v>
       </c>
       <c r="M61" s="3">
-        <v>710200</v>
+        <v>676400</v>
       </c>
       <c r="N61" s="3">
         <v>710200</v>
       </c>
       <c r="O61" s="3">
+        <v>710200</v>
+      </c>
+      <c r="P61" s="3">
         <v>722000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>561400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E62" s="3">
         <v>61900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>23400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>14800</v>
       </c>
       <c r="L62" s="3">
         <v>14800</v>
       </c>
       <c r="M62" s="3">
-        <v>133100</v>
+        <v>14800</v>
       </c>
       <c r="N62" s="3">
         <v>133100</v>
       </c>
       <c r="O62" s="3">
+        <v>133100</v>
+      </c>
+      <c r="P62" s="3">
         <v>162200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>158500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,55 +3323,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6461100</v>
+      </c>
+      <c r="E66" s="3">
         <v>6450500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6521800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6645000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4136100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4161500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>4550700</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2082100</v>
       </c>
       <c r="L66" s="3">
         <v>2082100</v>
       </c>
       <c r="M66" s="3">
-        <v>2115000</v>
+        <v>2082100</v>
       </c>
       <c r="N66" s="3">
         <v>2115000</v>
       </c>
       <c r="O66" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="P66" s="3">
         <v>2187300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1976300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,55 +3593,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12788300</v>
+      </c>
+      <c r="E72" s="3">
         <v>13101400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12951700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12961500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12110100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11421900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>11678700</v>
-      </c>
-      <c r="K72" s="3">
-        <v>2039800</v>
       </c>
       <c r="L72" s="3">
         <v>2039800</v>
       </c>
       <c r="M72" s="3">
-        <v>1890900</v>
+        <v>2039800</v>
       </c>
       <c r="N72" s="3">
         <v>1890900</v>
       </c>
       <c r="O72" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="P72" s="3">
         <v>1791200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1876700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,55 +3793,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12590300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12745300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12606000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12616400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12138700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11570600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>11789900</v>
-      </c>
-      <c r="K76" s="3">
-        <v>2072900</v>
       </c>
       <c r="L76" s="3">
         <v>2072900</v>
       </c>
       <c r="M76" s="3">
-        <v>1962100</v>
+        <v>2072900</v>
       </c>
       <c r="N76" s="3">
         <v>1962100</v>
       </c>
       <c r="O76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="P76" s="3">
         <v>1878200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1988100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,60 +3893,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45291</v>
       </c>
       <c r="L80" s="2">
         <v>45291</v>
       </c>
       <c r="M80" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="N80" s="2">
         <v>45107</v>
       </c>
       <c r="O80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3803,8 +3998,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,55 +4020,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E83" s="3">
         <v>68200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>64400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>47100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>154900</v>
       </c>
       <c r="L83" s="3">
         <v>154900</v>
       </c>
       <c r="M83" s="3">
-        <v>53000</v>
+        <v>154900</v>
       </c>
       <c r="N83" s="3">
         <v>53000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="O83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3">
         <v>158500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>192700</v>
+      </c>
+      <c r="E89" s="3">
         <v>385300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>547700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>375900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>237300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>292900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>376700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>166400</v>
       </c>
       <c r="L89" s="3">
         <v>166400</v>
       </c>
       <c r="M89" s="3">
-        <v>165700</v>
+        <v>166400</v>
       </c>
       <c r="N89" s="3">
         <v>165700</v>
       </c>
       <c r="O89" s="3">
+        <v>165700</v>
+      </c>
+      <c r="P89" s="3">
         <v>45800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>83900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,55 +4390,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-91200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-230700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-111800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-85300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-131300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-96100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-72400</v>
       </c>
       <c r="L91" s="3">
         <v>-72400</v>
       </c>
       <c r="M91" s="3">
-        <v>-75400</v>
+        <v>-72400</v>
       </c>
       <c r="N91" s="3">
         <v>-75400</v>
       </c>
       <c r="O91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="P91" s="3">
         <v>-60500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-119300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-265600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-193600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1810200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-101700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-52000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-89400</v>
       </c>
       <c r="L94" s="3">
         <v>-89400</v>
       </c>
       <c r="M94" s="3">
-        <v>-103300</v>
+        <v>-89400</v>
       </c>
       <c r="N94" s="3">
         <v>-103300</v>
       </c>
       <c r="O94" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="P94" s="3">
         <v>-49400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,55 +4610,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>305700</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>164600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>308200</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>139300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>133800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>172500</v>
       </c>
       <c r="L96" s="3">
         <v>172500</v>
       </c>
       <c r="M96" s="3">
-        <v>100</v>
+        <v>172500</v>
       </c>
       <c r="N96" s="3">
         <v>100</v>
       </c>
       <c r="O96" s="3">
+        <v>100</v>
+      </c>
+      <c r="P96" s="3">
         <v>242400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,145 +4808,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-119900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-412900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1537800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-110400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-125100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-233100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-303800</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-82300</v>
       </c>
       <c r="L100" s="3">
         <v>-82300</v>
       </c>
       <c r="M100" s="3">
-        <v>-66800</v>
+        <v>-82300</v>
       </c>
       <c r="N100" s="3">
         <v>-66800</v>
       </c>
       <c r="O100" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="P100" s="3">
         <v>14400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-6500</v>
       </c>
       <c r="L101" s="3">
         <v>-6500</v>
       </c>
       <c r="M101" s="3">
-        <v>3100</v>
+        <v>-6500</v>
       </c>
       <c r="N101" s="3">
         <v>3100</v>
       </c>
       <c r="O101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-55000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>92400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51400</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-8700</v>
       </c>
       <c r="L102" s="3">
         <v>-8700</v>
       </c>
       <c r="M102" s="3">
-        <v>-7600</v>
+        <v>-8700</v>
       </c>
       <c r="N102" s="3">
         <v>-7600</v>
       </c>
       <c r="O102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="P102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>48000</v>
       </c>
     </row>
